--- a/utils/tstart-tend.xlsx
+++ b/utils/tstart-tend.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leroquan\Documents\python\preprocessing-mitgcm\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80384A03-15F5-4BA0-AA04-6F8B4F74E925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9814A565-A81D-491D-803B-89859F21A4B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="7" xr2:uid="{1C1AAA8F-B7A7-4F2E-9366-9D04187454FC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="7" xr2:uid="{1C1AAA8F-B7A7-4F2E-9366-9D04187454FC}"/>
   </bookViews>
   <sheets>
     <sheet name="13.08.2023" sheetId="1" r:id="rId1"/>
@@ -105,9 +105,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -439,13 +438,13 @@
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>45151</v>
       </c>
       <c r="F2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>45151</v>
       </c>
     </row>
@@ -453,13 +452,13 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <v>4</v>
       </c>
       <c r="F3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3">
         <f>C3</f>
         <v>4</v>
       </c>
@@ -468,13 +467,13 @@
       <c r="B4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>668250</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>45170</v>
       </c>
     </row>
@@ -488,10 +487,10 @@
       <c r="F5" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>45182</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <f>G5-J5</f>
         <v>45163</v>
       </c>
@@ -504,7 +503,7 @@
       <c r="B6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6">
         <v>668250</v>
       </c>
     </row>
@@ -512,7 +511,7 @@
       <c r="F8" t="s">
         <v>0</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8">
         <f>(G4-$G$2)*24*60*60</f>
         <v>1641600</v>
       </c>
@@ -521,14 +520,14 @@
       <c r="B9" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <f>$C$2+C4/(24*60*60)</f>
         <v>45158.734375</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9">
         <f>(G5-$G$2)*24*60*60</f>
         <v>2678400</v>
       </c>
@@ -537,7 +536,7 @@
       <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <f>$C$2+C5/(24*60*60)</f>
         <v>45237</v>
       </c>
@@ -555,13 +554,13 @@
       <c r="B12" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f>$C$2+C6/(24*60*60)*C3</f>
         <v>45181.9375</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="C13" s="3"/>
+      <c r="C13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -582,13 +581,13 @@
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>45212</v>
       </c>
       <c r="F2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <f>C2</f>
         <v>45212</v>
       </c>
@@ -597,13 +596,13 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <v>4</v>
       </c>
       <c r="F3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3">
         <f>C3</f>
         <v>4</v>
       </c>
@@ -612,13 +611,13 @@
       <c r="B4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>668250</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>45227</v>
       </c>
     </row>
@@ -632,10 +631,10 @@
       <c r="F5" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>45238</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <f>G5-J5</f>
         <v>45223</v>
       </c>
@@ -648,7 +647,7 @@
       <c r="B6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6">
         <v>581850</v>
       </c>
     </row>
@@ -656,7 +655,7 @@
       <c r="F8" t="s">
         <v>0</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8">
         <f>(G4-$G$2)*24*60*60</f>
         <v>1296000</v>
       </c>
@@ -665,14 +664,14 @@
       <c r="B9" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <f>$C$2+C4/(24*60*60)</f>
         <v>45219.734375</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9">
         <f>(G5-$G$2)*24*60*60</f>
         <v>2246400</v>
       </c>
@@ -681,7 +680,7 @@
       <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <f>$C$2+C5/(24*60*60)</f>
         <v>45298</v>
       </c>
@@ -699,7 +698,7 @@
       <c r="B12" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f>$C$2+C6/(24*60*60)*C3</f>
         <v>45238.9375</v>
       </c>
@@ -723,13 +722,13 @@
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>45389</v>
       </c>
       <c r="F2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <f>C2</f>
         <v>45389</v>
       </c>
@@ -738,13 +737,13 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <v>4</v>
       </c>
       <c r="F3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3">
         <f>C3</f>
         <v>4</v>
       </c>
@@ -753,13 +752,13 @@
       <c r="B4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>668250</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>45402</v>
       </c>
     </row>
@@ -773,10 +772,10 @@
       <c r="F5" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>45414</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <f>G5-J5</f>
         <v>45401</v>
       </c>
@@ -789,7 +788,7 @@
       <c r="B6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6">
         <v>280800</v>
       </c>
     </row>
@@ -797,7 +796,7 @@
       <c r="F8" t="s">
         <v>0</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8">
         <f>(G4-$G$2)*24*60*60</f>
         <v>1123200</v>
       </c>
@@ -806,14 +805,14 @@
       <c r="B9" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <f>$C$2+C4/(24*60*60)</f>
         <v>45396.734375</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9">
         <f>(G5-$G$2)*24*60*60</f>
         <v>2160000</v>
       </c>
@@ -822,7 +821,7 @@
       <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <f>$C$2+C5/(24*60*60)</f>
         <v>45475</v>
       </c>
@@ -840,7 +839,7 @@
       <c r="B12" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f>$C$2+C6/(24*60*60)*C3</f>
         <v>45402</v>
       </c>
@@ -866,14 +865,14 @@
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <f>G2</f>
         <v>45352</v>
       </c>
       <c r="F2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>45352</v>
       </c>
     </row>
@@ -881,14 +880,14 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <f>G3</f>
         <v>32</v>
       </c>
       <c r="F3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3">
         <v>32</v>
       </c>
     </row>
@@ -896,13 +895,13 @@
       <c r="B4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>4752000</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>45512</v>
       </c>
     </row>
@@ -916,10 +915,10 @@
       <c r="F5" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>45658</v>
       </c>
-      <c r="I5" s="3"/>
+      <c r="I5" s="2"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
@@ -933,7 +932,7 @@
       <c r="F8" t="s">
         <v>0</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8">
         <f>(G4-$G$2)*24*60*60</f>
         <v>13824000</v>
       </c>
@@ -942,14 +941,14 @@
       <c r="B9" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <f>$C$2+C4/(24*60*60)</f>
         <v>45407</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9">
         <f>(G5-$G$2)*24*60*60</f>
         <v>26438400</v>
       </c>
@@ -958,7 +957,7 @@
       <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <f>$C$2+C5/(24*60*60)</f>
         <v>45514</v>
       </c>
@@ -976,7 +975,7 @@
       <c r="B12" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f>$C$2+C6/(24*60*60)*$C$3</f>
         <v>45512</v>
       </c>
@@ -1001,14 +1000,14 @@
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <f>G2</f>
         <v>45778</v>
       </c>
       <c r="F2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>45778</v>
       </c>
     </row>
@@ -1016,14 +1015,14 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <f>G3</f>
         <v>32</v>
       </c>
       <c r="F3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3">
         <v>32</v>
       </c>
     </row>
@@ -1031,13 +1030,13 @@
       <c r="B4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>4752000</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>45172</v>
       </c>
     </row>
@@ -1051,7 +1050,7 @@
       <c r="F5" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>45182</v>
       </c>
     </row>
@@ -1067,7 +1066,7 @@
       <c r="F8" t="s">
         <v>0</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8">
         <f>(G4-$G$2)*24*60*60</f>
         <v>-52358400</v>
       </c>
@@ -1076,14 +1075,14 @@
       <c r="B9" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <f>$C$2+C4/(24*60*60)</f>
         <v>45833</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9">
         <f>(G5-$G$2)*24*60*60</f>
         <v>-51494400</v>
       </c>
@@ -1092,7 +1091,7 @@
       <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <f>$C$2+C5/(24*60*60)</f>
         <v>45864</v>
       </c>
@@ -1110,7 +1109,7 @@
       <c r="B12" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f>$C$2+C6/(24*60*60)*4</f>
         <v>45796.375</v>
       </c>
@@ -1136,13 +1135,13 @@
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3">
-        <v>45261</v>
+      <c r="C2" s="2">
+        <v>45658</v>
       </c>
       <c r="F2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>45261</v>
       </c>
     </row>
@@ -1150,13 +1149,13 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1">
-        <v>4</v>
+      <c r="C3">
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3">
         <v>4</v>
       </c>
     </row>
@@ -1164,13 +1163,13 @@
       <c r="B4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>4752000</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>45172</v>
       </c>
     </row>
@@ -1184,24 +1183,24 @@
       <c r="F5" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>45182</v>
       </c>
-      <c r="I5" s="3"/>
+      <c r="I5" s="2"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6">
-        <v>8176950</v>
+        <v>3144960</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="F8" t="s">
         <v>0</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8">
         <f>(G4-$G$2)*24*60*60</f>
         <v>-7689600</v>
       </c>
@@ -1210,14 +1209,14 @@
       <c r="B9" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <f>$C$2+C4/(24*60*60)</f>
-        <v>45316</v>
+        <v>45713</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9">
         <f>(G5-$G$2)*24*60*60</f>
         <v>-6825600</v>
       </c>
@@ -1226,9 +1225,9 @@
       <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <f>$C$2+C5/(24*60*60)</f>
-        <v>45347</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.35">
@@ -1244,9 +1243,9 @@
       <c r="B12" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="3">
-        <f>$C$2+C6/(24*60*60)*4</f>
-        <v>45639.5625</v>
+      <c r="C12" s="2">
+        <f>$C$2+C6/(24*60*60)*C3</f>
+        <v>46022</v>
       </c>
     </row>
   </sheetData>
@@ -1268,14 +1267,14 @@
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <f>G2</f>
         <v>46023</v>
       </c>
       <c r="F2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>46023</v>
       </c>
     </row>
@@ -1283,14 +1282,14 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <f>G3</f>
         <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3">
         <v>10</v>
       </c>
     </row>
@@ -1298,13 +1297,13 @@
       <c r="B4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>4752000</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>45770</v>
       </c>
     </row>
@@ -1318,7 +1317,7 @@
       <c r="F5" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>45962</v>
       </c>
     </row>
@@ -1334,7 +1333,7 @@
       <c r="F8" t="s">
         <v>0</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8">
         <f>(G4-$G$2)*24*60*60</f>
         <v>-21859200</v>
       </c>
@@ -1343,14 +1342,14 @@
       <c r="B9" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <f>$C$2+C4/(24*60*60)</f>
         <v>46078</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9">
         <f>(G5-$G$2)*24*60*60</f>
         <v>-5270400</v>
       </c>
@@ -1359,7 +1358,7 @@
       <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <f>$C$2+C5/(24*60*60)</f>
         <v>46298</v>
       </c>
@@ -1377,7 +1376,7 @@
       <c r="B12" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f>$C$2+C6/(24*60*60)*C3</f>
         <v>46045.979166666664</v>
       </c>
@@ -1389,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B99AB26-8EB3-493A-9F6D-78FC21FACCDC}">
-  <dimension ref="B2:G12"/>
+  <dimension ref="B2:H14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -1397,51 +1396,51 @@
     <col min="7" max="7" width="15.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <f>G2</f>
         <v>45658</v>
       </c>
       <c r="F2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>45658</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <f>G3</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="G3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>4752000</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3">
-        <v>45770</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="G4" s="2">
+        <v>46023.020833333336</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>1</v>
       </c>
@@ -1451,68 +1450,74 @@
       <c r="F5" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3">
-        <v>45962</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="G5" s="2">
+        <v>46025.8125</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6">
-        <v>4492800</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
+        <v>509580</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="F8" t="s">
         <v>0</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8">
         <f>(G4-$G$2)*24*60*60</f>
-        <v>9676800</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
+        <v>31537800.000000209</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <f>$C$2+C4/(24*60*60)</f>
         <v>45713</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9">
         <f>(G5-$G$2)*24*60*60</f>
-        <v>26265600</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
+        <v>31779000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <f>$C$2+C5/(24*60*60)</f>
         <v>45933</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
       <c r="F11" t="s">
         <v>4</v>
       </c>
       <c r="G11">
         <f>G8/$G$3</f>
-        <v>1382400</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
+        <v>3153780.000000021</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f>$C$2+C6/(24*60*60)*C3</f>
-        <v>46022</v>
+        <v>45716.979166666664</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="H14">
+        <f>30*2*24*2</f>
+        <v>2880</v>
       </c>
     </row>
   </sheetData>
